--- a/Result/profitability/8213.xlsx
+++ b/Result/profitability/8213.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.71875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.2975</v>
+        <v>12.05625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.825</v>
+        <v>0.80125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.465</v>
+        <v>12.33125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.81625</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>12.545</v>
+        <v>12.61</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.89375</v>
+        <v>0.8975</v>
       </c>
       <c r="N5" t="n">
-        <v>13.67</v>
+        <v>13.45</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9225</v>
+        <v>0.93375</v>
       </c>
       <c r="N6" t="n">
-        <v>14.095</v>
+        <v>14.14875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.89</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09125</v>
+        <v>1.10875</v>
       </c>
       <c r="N7" t="n">
-        <v>15.6325</v>
+        <v>15.67625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>1.29875</v>
+        <v>1.34</v>
       </c>
       <c r="N8" t="n">
-        <v>17.0375</v>
+        <v>17.13875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8213</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5303</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4699</v>
+      </c>
+      <c r="E74" t="n">
+        <v>604</v>
+      </c>
+      <c r="F74" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G74" t="n">
+        <v>247</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>4.67%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>252</v>
+      </c>
+      <c r="K74" t="n">
+        <v>171</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="N74" t="n">
+        <v>11.73125</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0.8100000000000005</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.07648725212464602</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-0.1337386018237082</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
